--- a/Inventory/Assets/Excel/ExcelData.xlsx
+++ b/Inventory/Assets/Excel/ExcelData.xlsx
@@ -8,15 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\Inventory\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148011AF-ECF5-4100-AAD6-A20CD0664554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B456FA7-5D1A-495A-9032-A8512F12A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Common" sheetId="1" r:id="rId1"/>
-    <sheet name="Rare" sheetId="2" r:id="rId2"/>
-    <sheet name="Unique" sheetId="4" r:id="rId3"/>
-    <sheet name="Legendary" sheetId="5" r:id="rId4"/>
+    <sheet name="Object" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -54,75 +51,36 @@
     <t>height</t>
   </si>
   <si>
-    <t>displayName</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>c</t>
+    <t>1×1</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>d</t>
+    <t>1×1_body</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>e</t>
+    <t>1×1_gauntlet</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>f</t>
+    <t>1×1_head</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>g</t>
+    <t>1×1_shoes</t>
+  </si>
+  <si>
+    <t>1×1_Weapon</t>
+  </si>
+  <si>
+    <t>1×2</t>
+  </si>
+  <si>
+    <t>equipmentType</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>A</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>E</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>G</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>H</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>rare</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>rareName</t>
+    <t>typeName</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -502,16 +460,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="11.125" customWidth="1"/>
     <col min="7" max="7" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,214 +484,167 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2" t="str">
-        <f>IF($E2 =0, "Common", IF($E2 = 1, "Rare", IF($E2 = 2, "Unique", "Legendary")))</f>
-        <v>Common</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
+        <f>IF(E2=0,"Helmet",IF(E2=1,"Armor",IF(E2=2,"Gauntlet",IF(E2=3,"Shoes",IF(E2=4,"Weapon","None")))))</f>
+        <v>None</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F9" si="0">IF($E3 =0, "Common", IF($E3 = 1, "Rare", IF($E3 = 2, "Unique", "Legendary")))</f>
-        <v>Rare</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
+        <f t="shared" ref="F3:F8" si="0">IF(E3=0,"Helmet",IF(E3=1,"Armor",IF(E3=2,"Gauntlet",IF(E3=3,"Shoes",IF(E3=4,"Weapon","None")))))</f>
+        <v>Armor</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
-        <v>Unique</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
+        <v>Gauntlet</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="str">
-        <f>IF($E5 =0, "Common", IF($E5 = 1, "Rare", IF($E5 = 2, "Unique", "Legendary")))</f>
-        <v>Legendary</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>Helmet</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
-        <v>Common</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
+        <v>Shoes</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
-        <v>Common</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
+        <v>Weapon</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
-        <v>Common</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
+        <v>None</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" si="0"/>
-        <v>Common</v>
-      </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="19" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -825,34 +737,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EEE665-9A6E-4ADB-B90C-60DD148E0C8B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80009E1A-90E9-463E-8301-859820CB9A5F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8AB2ED6-AB54-44EC-94D3-9BE7F15EB5D4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Inventory/Assets/Excel/ExcelData.xlsx
+++ b/Inventory/Assets/Excel/ExcelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\Inventory\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B456FA7-5D1A-495A-9032-A8512F12A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F4F011-341D-4116-94AC-6B0D06D5299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Inventory/Assets/Excel/ExcelData.xlsx
+++ b/Inventory/Assets/Excel/ExcelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\Inventory\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F4F011-341D-4116-94AC-6B0D06D5299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B456FA7-5D1A-495A-9032-A8512F12A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
